--- a/AtchisonRegime/Outputs/Canada/df_regLTRates_Canada.xlsx
+++ b/AtchisonRegime/Outputs/Canada/df_regLTRates_Canada.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H629"/>
+  <dimension ref="A1:H630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16804,6 +16804,32 @@
         <v>1</v>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B630" t="n">
+        <v>2.889354</v>
+      </c>
+      <c r="C630" t="n">
+        <v>2.922454333333334</v>
+      </c>
+      <c r="D630" t="n">
+        <v>2.976221</v>
+      </c>
+      <c r="E630" t="n">
+        <v>0.3750805556492636</v>
+      </c>
+      <c r="F630" t="b">
+        <v>0</v>
+      </c>
+      <c r="G630" t="n">
+        <v>-0.1433469846859853</v>
+      </c>
+      <c r="H630" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
